--- a/content/dramas.xlsx
+++ b/content/dramas.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dramas" sheetId="1" r:id="R5fdffe6362eb44ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dramas" sheetId="1" r:id="R5882a7c04a81451d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -348,426 +348,746 @@
         <x:v>标签4</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="42" customHeight="1">
+    <x:row r="2" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A2" s="8" t="str">
         <x:v>1a</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>Hidden Daughter</x:v>
-      </x:c>
-      <x:c r="C2" s="10"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-      <x:c r="G2" s="9"/>
-    </x:row>
-    <x:row r="3" ht="42" customHeight="1">
+        <x:v>After the Divorce, I Took Back My Company and My Name</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="str">
+        <x:v>When her husband demands a divorce, Claire discovers that the company they built together has quietly become his alone. Shut out of the boardroom and blamed for its failures, she refuses the generous settlement meant to buy her silence. With an overlooked contract and an unexpected ally, Claire begins rebuilding her career while uncovering how her marriage became a business arrangement. Her former husband is determined to protect his reputation, even if it means destroying hers. As a crucial shareholder meeting approaches, Claire must decide how much she is willing to risk to reclaim her work, her independence, and her name......</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>Drama</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>Revenge</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>Divorce</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A3" s="8" t="str">
         <x:v>1b</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>Hidden Daughter Returns to a Family Full of Lies</x:v>
-      </x:c>
-      <x:c r="C3" s="10"/>
-      <x:c r="D3" s="9"/>
-      <x:c r="E3" s="9"/>
-      <x:c r="F3" s="9"/>
-      <x:c r="G3" s="9"/>
-    </x:row>
-    <x:row r="4" ht="42" customHeight="1">
+        <x:v>Took Everything Back After Divorce</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
+        <x:v>When her husband demands a divorce, Claire discovers that the company they built together has quietly become his alone. Shut out of the boardroom and blamed for its failures, she refuses the generous settlement meant to buy her silence. With an overlooked contract and an unexpected ally, Claire begins rebuilding her career while uncovering how her marriage became a business arrangement. Her former husband is determined to protect his reputation, even if it means destroying hers. As a crucial shareholder meeting approaches, Claire must decide how much she is willing to risk to reclaim her work, her independence, and her name......</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="str">
+        <x:v>Drama</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="str">
+        <x:v>Revenge</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="str">
+        <x:v>Divorce</x:v>
+      </x:c>
+      <x:c r="G3" s="9" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="str">
         <x:v>2a</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>Stolen Life</x:v>
-      </x:c>
-      <x:c r="C4" s="10"/>
-      <x:c r="D4" s="9"/>
-      <x:c r="E4" s="9"/>
-      <x:c r="F4" s="9"/>
-      <x:c r="G4" s="9"/>
-    </x:row>
-    <x:row r="5" ht="42" customHeight="1">
+        <x:v>I Married the Vampire King to Save My Family From Ruin</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>To save her family from ruin, Elena accepts a marriage proposal from a stranger whose wealth comes with one condition: she must never enter the castle after midnight. Her new husband, a vampire king feared by his own court, seems more interested in an ancient agreement than in his bride. But Elena soon discovers that her arrival has disturbed a fragile peace, and that her family has hidden its connection to his kingdom. Caught between dangerous loyalties and an attraction she cannot explain, she must uncover why she was chosen before the marriage meant to protect her becomes the beginning of a war......</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>Romance</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="str">
+        <x:v>Fantasy</x:v>
+      </x:c>
+      <x:c r="F4" s="9" t="str">
+        <x:v>Vampire</x:v>
+      </x:c>
+      <x:c r="G4" s="9" t="str">
+        <x:v>Arranged Marriage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A5" s="8" t="str">
         <x:v>2b</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>Stolen Life Reveals the Lie Behind Our Perfect Family</x:v>
-      </x:c>
-      <x:c r="C5" s="10"/>
-      <x:c r="D5" s="9"/>
-      <x:c r="E5" s="9"/>
-      <x:c r="F5" s="9"/>
-      <x:c r="G5" s="9"/>
-    </x:row>
-    <x:row r="6" ht="42" customHeight="1">
+        <x:v>Married to the Vampire King</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="str">
+        <x:v>To save her family from ruin, Elena accepts a marriage proposal from a stranger whose wealth comes with one condition: she must never enter the castle after midnight. Her new husband, a vampire king feared by his own court, seems more interested in an ancient agreement than in his bride. But Elena soon discovers that her arrival has disturbed a fragile peace, and that her family has hidden its connection to his kingdom. Caught between dangerous loyalties and an attraction she cannot explain, she must uncover why she was chosen before the marriage meant to protect her becomes the beginning of a war......</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>Romance</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>Fantasy</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>Vampire</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="str">
+        <x:v>Arranged Marriage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A6" s="8" t="str">
         <x:v>3a</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>Broken Ties</x:v>
-      </x:c>
-      <x:c r="C6" s="10"/>
-      <x:c r="D6" s="9"/>
-      <x:c r="E6" s="9"/>
-      <x:c r="F6" s="9"/>
-      <x:c r="G6" s="9"/>
-    </x:row>
-    <x:row r="7" ht="42" customHeight="1">
+        <x:v>One Accidental Kiss with the Superstar Changed My Entire Life</x:v>
+      </x:c>
+      <x:c r="C6" s="10" t="str">
+        <x:v>An impulsive kiss outside a concert turns struggling stylist Mia into the most talked about woman in the country. The man she kissed is Adrian, a superstar whose carefully managed image leaves no room for unexpected romance. To contain the scandal, his team offers Mia a temporary arrangement that could rescue her career, provided she follows their rules. Behind closed doors, however, the celebrity she thought she understood reveals a very different life. As jealous rivals and relentless cameras close in, Mia must decide whether their growing connection is worth the cost of becoming part of a story everyone else wants to control......</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>Romance</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="str">
+        <x:v>Celebrity</x:v>
+      </x:c>
+      <x:c r="F6" s="9" t="str">
+        <x:v>Secret Relationship</x:v>
+      </x:c>
+      <x:c r="G6" s="9" t="str">
+        <x:v>Showbiz</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A7" s="8" t="str">
         <x:v>3b</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>Broken Ties Resurface as the Missing Son Returns</x:v>
-      </x:c>
-      <x:c r="C7" s="10"/>
-      <x:c r="D7" s="9"/>
-      <x:c r="E7" s="9"/>
-      <x:c r="F7" s="9"/>
-      <x:c r="G7" s="9"/>
-    </x:row>
-    <x:row r="8" ht="42" customHeight="1">
+        <x:v>One Kiss with a Superstar</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
+        <x:v>An impulsive kiss outside a concert turns struggling stylist Mia into the most talked about woman in the country. The man she kissed is Adrian, a superstar whose carefully managed image leaves no room for unexpected romance. To contain the scandal, his team offers Mia a temporary arrangement that could rescue her career, provided she follows their rules. Behind closed doors, however, the celebrity she thought she understood reveals a very different life. As jealous rivals and relentless cameras close in, Mia must decide whether their growing connection is worth the cost of becoming part of a story everyone else wants to control......</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>Romance</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str">
+        <x:v>Celebrity</x:v>
+      </x:c>
+      <x:c r="F7" s="9" t="str">
+        <x:v>Secret Relationship</x:v>
+      </x:c>
+      <x:c r="G7" s="9" t="str">
+        <x:v>Showbiz</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A8" s="8" t="str">
         <x:v>4a</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>Silent Dynasty</x:v>
-      </x:c>
-      <x:c r="C8" s="10"/>
-      <x:c r="D8" s="9"/>
-      <x:c r="E8" s="9"/>
-      <x:c r="F8" s="9"/>
-      <x:c r="G8" s="9"/>
-    </x:row>
-    <x:row r="9" ht="42" customHeight="1">
+        <x:v>When My Husband Chose His Mother Over Us, I Took the Kids and Started Over</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>For years, Naomi has kept the peace between her husband and his demanding mother, even when it means putting her own children last. One humiliating evening finally forces her to leave the family home with two suitcases and no clear plan. Starting again brings unfamiliar work, a cramped apartment, and questions her children are too young to answer. Meanwhile, her husband struggles to understand why an apology cannot undo years of silence. When a custody dispute draws the entire family into conflict, Naomi must protect the life she is building while deciding what reconciliation would actually require from the people who want her back......</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="str">
+        <x:v>Marriage</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="str">
+        <x:v>Motherhood</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="str">
+        <x:v>New Beginnings</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A9" s="8" t="str">
         <x:v>4b</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>Silent Dynasty Falls When the Missing Son Comes Home</x:v>
-      </x:c>
-      <x:c r="C9" s="10"/>
-      <x:c r="D9" s="9"/>
-      <x:c r="E9" s="9"/>
-      <x:c r="F9" s="9"/>
-      <x:c r="G9" s="9"/>
-    </x:row>
-    <x:row r="10" ht="42" customHeight="1">
+        <x:v>Our Family Finally Faced the Truth</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
+        <x:v>For years, Naomi has kept the peace between her husband and his demanding mother, even when it means putting her own children last. One humiliating evening finally forces her to leave the family home with two suitcases and no clear plan. Starting again brings unfamiliar work, a cramped apartment, and questions her children are too young to answer. Meanwhile, her husband struggles to understand why an apology cannot undo years of silence. When a custody dispute draws the entire family into conflict, Naomi must protect the life she is building while deciding what reconciliation would actually require from the people who want her back......</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="str">
+        <x:v>Marriage</x:v>
+      </x:c>
+      <x:c r="F9" s="9" t="str">
+        <x:v>Motherhood</x:v>
+      </x:c>
+      <x:c r="G9" s="9" t="str">
+        <x:v>New Beginnings</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A10" s="8" t="str">
         <x:v>5a</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>Bloodlines</x:v>
-      </x:c>
-      <x:c r="C10" s="10"/>
-      <x:c r="D10" s="9"/>
-      <x:c r="E10" s="9"/>
-      <x:c r="F10" s="9"/>
-      <x:c r="G10" s="9"/>
-    </x:row>
-    <x:row r="11" ht="42" customHeight="1">
+        <x:v>On My Wedding Day, I Learned My Sister Was Hiding Our Mother’s Greatest Secret</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>Hours before her wedding, Sophie finds a letter hidden inside her sister's bag that challenges everything she believes about their mother. Her sister begs her to forget it until the ceremony is over, but an unfamiliar guest arrives with a different version of the past. As the celebration continues, Sophie begins noticing the conversations that stop when she enters and the promises nobody will explain. Determined to find answers, she risks alienating the people who have planned every detail of her future. Before she walks down the aisle, Sophie must choose whom to trust and whether her family can survive an honest conversation......</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="str">
+        <x:v>Wedding</x:v>
+      </x:c>
+      <x:c r="F10" s="9" t="str">
+        <x:v>Family Secrets</x:v>
+      </x:c>
+      <x:c r="G10" s="9" t="str">
+        <x:v>Sisterhood</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A11" s="8" t="str">
         <x:v>5b</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>Bloodlines Fracture When the Will Names a Stranger</x:v>
-      </x:c>
-      <x:c r="C11" s="10"/>
-      <x:c r="D11" s="9"/>
-      <x:c r="E11" s="9"/>
-      <x:c r="F11" s="9"/>
-      <x:c r="G11" s="9"/>
-    </x:row>
-    <x:row r="12" ht="42" customHeight="1">
+        <x:v>My Sister’s Secret at the Wedding</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>Hours before her wedding, Sophie finds a letter hidden inside her sister's bag that challenges everything she believes about their mother. Her sister begs her to forget it until the ceremony is over, but an unfamiliar guest arrives with a different version of the past. As the celebration continues, Sophie begins noticing the conversations that stop when she enters and the promises nobody will explain. Determined to find answers, she risks alienating the people who have planned every detail of her future. Before she walks down the aisle, Sophie must choose whom to trust and whether her family can survive an honest conversation......</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="str">
+        <x:v>Wedding</x:v>
+      </x:c>
+      <x:c r="F11" s="9" t="str">
+        <x:v>Family Secrets</x:v>
+      </x:c>
+      <x:c r="G11" s="9" t="str">
+        <x:v>Sisterhood</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A12" s="8" t="str">
         <x:v>6a</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>Home Truths</x:v>
-      </x:c>
-      <x:c r="C12" s="10"/>
-      <x:c r="D12" s="9"/>
-      <x:c r="E12" s="9"/>
-      <x:c r="F12" s="9"/>
-      <x:c r="G12" s="9"/>
-    </x:row>
-    <x:row r="13" ht="42" customHeight="1">
+        <x:v>When His Family Tore Us Apart, I Had to Choose Myself and My Son</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str">
+        <x:v>After another argument ends with her husband's relatives deciding what is best for her son, Anna realizes that staying together has begun to mean disappearing. She leaves the family estate and accepts a job in a town where nobody knows her married name. While her son adjusts to a new school, Anna faces financial pressure, persistent relatives, and a husband who insists that love should be enough to bring her home. An unexpected opportunity offers the independence she has wanted for years, but accepting it could make their separation permanent. Now she must decide what kind of future she wants them to share......</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="str">
+        <x:v>Marriage</x:v>
+      </x:c>
+      <x:c r="F12" s="9" t="str">
+        <x:v>Motherhood</x:v>
+      </x:c>
+      <x:c r="G12" s="9" t="str">
+        <x:v>Self-Discovery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A13" s="8" t="str">
         <x:v>6b</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>Home Truths Emerge as Our Mother Reveals Another Family</x:v>
-      </x:c>
-      <x:c r="C13" s="10"/>
-      <x:c r="D13" s="9"/>
-      <x:c r="E13" s="9"/>
-      <x:c r="F13" s="9"/>
-      <x:c r="G13" s="9"/>
-    </x:row>
-    <x:row r="14" ht="42" customHeight="1">
+        <x:v>Choosing Myself and My Son</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str">
+        <x:v>After another argument ends with her husband's relatives deciding what is best for her son, Anna realizes that staying together has begun to mean disappearing. She leaves the family estate and accepts a job in a town where nobody knows her married name. While her son adjusts to a new school, Anna faces financial pressure, persistent relatives, and a husband who insists that love should be enough to bring her home. An unexpected opportunity offers the independence she has wanted for years, but accepting it could make their separation permanent. Now she must decide what kind of future she wants them to share......</x:v>
+      </x:c>
+      <x:c r="D13" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E13" s="9" t="str">
+        <x:v>Marriage</x:v>
+      </x:c>
+      <x:c r="F13" s="9" t="str">
+        <x:v>Motherhood</x:v>
+      </x:c>
+      <x:c r="G13" s="9" t="str">
+        <x:v>Self-Discovery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A14" s="8" t="str">
         <x:v>7a</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>Behind Closed Doors</x:v>
-      </x:c>
-      <x:c r="C14" s="10"/>
-      <x:c r="D14" s="9"/>
-      <x:c r="E14" s="9"/>
-      <x:c r="F14" s="9"/>
-      <x:c r="G14" s="9"/>
-    </x:row>
-    <x:row r="15" ht="42" customHeight="1">
+        <x:v>After the Divorce, I Fell for My Ex-Husband’s Rival</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str">
+        <x:v>Fresh from a painful divorce, Lily accepts a consulting role without realizing that her new client is the businessman her former husband hates most. Daniel is sharp, demanding, and unwilling to discuss the rivalry that shadows every meeting. Their uneasy partnership begins to change as Lily discovers how much of her marriage was shaped by stories she never questioned. But a major deal puts her between the two men, and her growing feelings threaten to make every professional decision look personal. When private messages reach the press, Lily must defend her work and decide whether starting over means trusting someone she was taught to distrust......</x:v>
+      </x:c>
+      <x:c r="D14" s="9" t="str">
+        <x:v>Romance</x:v>
+      </x:c>
+      <x:c r="E14" s="9" t="str">
+        <x:v>Divorce</x:v>
+      </x:c>
+      <x:c r="F14" s="9" t="str">
+        <x:v>Forbidden Love</x:v>
+      </x:c>
+      <x:c r="G14" s="9" t="str">
+        <x:v>Business Rivals</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A15" s="8" t="str">
         <x:v>7b</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>Behind Closed Doors, Every Promise Hides a Betrayal</x:v>
-      </x:c>
-      <x:c r="C15" s="10"/>
-      <x:c r="D15" s="9"/>
-      <x:c r="E15" s="9"/>
-      <x:c r="F15" s="9"/>
-      <x:c r="G15" s="9"/>
-    </x:row>
-    <x:row r="16" ht="42" customHeight="1">
+        <x:v>Falling for My Ex’s Rival</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str">
+        <x:v>Fresh from a painful divorce, Lily accepts a consulting role without realizing that her new client is the businessman her former husband hates most. Daniel is sharp, demanding, and unwilling to discuss the rivalry that shadows every meeting. Their uneasy partnership begins to change as Lily discovers how much of her marriage was shaped by stories she never questioned. But a major deal puts her between the two men, and her growing feelings threaten to make every professional decision look personal. When private messages reach the press, Lily must defend her work and decide whether starting over means trusting someone she was taught to distrust......</x:v>
+      </x:c>
+      <x:c r="D15" s="9" t="str">
+        <x:v>Romance</x:v>
+      </x:c>
+      <x:c r="E15" s="9" t="str">
+        <x:v>Divorce</x:v>
+      </x:c>
+      <x:c r="F15" s="9" t="str">
+        <x:v>Forbidden Love</x:v>
+      </x:c>
+      <x:c r="G15" s="9" t="str">
+        <x:v>Business Rivals</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A16" s="8" t="str">
         <x:v>8a</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>Power Within</x:v>
-      </x:c>
-      <x:c r="C16" s="10"/>
-      <x:c r="D16" s="9"/>
-      <x:c r="E16" s="9"/>
-      <x:c r="F16" s="9"/>
-      <x:c r="G16" s="9"/>
-    </x:row>
-    <x:row r="17" ht="42" customHeight="1">
+        <x:v>My Mother-in-Law Tried to Ruin Our Marriage</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str">
+        <x:v>Moving into her husband's family home seems like a practical way for Eva and Marcus to save for their future. Instead, every meal, purchase, and private disagreement becomes a matter for his mother to settle. Eva tries to establish boundaries, while Marcus insists that the tension will pass if everyone makes an effort. Then an incident at a family celebration reveals that their problems began long before Eva arrived. As alliances shift and old resentments surface, the couple must confront the expectations they brought into their marriage. Saving their relationship may depend on whether they can finally make decisions without asking anyone else's permission......</x:v>
+      </x:c>
+      <x:c r="D16" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E16" s="9" t="str">
+        <x:v>Romance</x:v>
+      </x:c>
+      <x:c r="F16" s="9" t="str">
+        <x:v>Marriage</x:v>
+      </x:c>
+      <x:c r="G16" s="9" t="str">
+        <x:v>Family Conflict</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A17" s="8" t="str">
         <x:v>8b</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>Power Within Keeps the Family’s Crime Buried</x:v>
-      </x:c>
-      <x:c r="C17" s="10"/>
-      <x:c r="D17" s="9"/>
-      <x:c r="E17" s="9"/>
-      <x:c r="F17" s="9"/>
-      <x:c r="G17" s="9"/>
-    </x:row>
-    <x:row r="18" ht="42" customHeight="1">
+        <x:v>At War with My Mother-in-Law</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str">
+        <x:v>Moving into her husband's family home seems like a practical way for Eva and Marcus to save for their future. Instead, every meal, purchase, and private disagreement becomes a matter for his mother to settle. Eva tries to establish boundaries, while Marcus insists that the tension will pass if everyone makes an effort. Then an incident at a family celebration reveals that their problems began long before Eva arrived. As alliances shift and old resentments surface, the couple must confront the expectations they brought into their marriage. Saving their relationship may depend on whether they can finally make decisions without asking anyone else's permission......</x:v>
+      </x:c>
+      <x:c r="D17" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E17" s="9" t="str">
+        <x:v>Romance</x:v>
+      </x:c>
+      <x:c r="F17" s="9" t="str">
+        <x:v>Marriage</x:v>
+      </x:c>
+      <x:c r="G17" s="9" t="str">
+        <x:v>Family Conflict</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A18" s="8" t="str">
         <x:v>9a</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>Deadly Manor</x:v>
-      </x:c>
-      <x:c r="C18" s="10"/>
-      <x:c r="D18" s="9"/>
-      <x:c r="E18" s="9"/>
-      <x:c r="F18" s="9"/>
-      <x:c r="G18" s="9"/>
-    </x:row>
-    <x:row r="19" ht="42" customHeight="1">
+        <x:v>One Kiss with My Bodyguard Changed Everything</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str">
+        <x:v>After a threatening message interrupts an awards ceremony, rising singer Serena is assigned a bodyguard who refuses to be charmed by fame. Ethan keeps his distance, follows every rule, and notices details that her closest friends overlook. A kiss meant to distract a photographer changes their arrangement, making the line between protection and desire harder to maintain. When another warning exposes a connection to Serena's past, even the people managing her career become suspects. Forced into an uneasy retreat from public life, she must decide whether to trust Ethan with the secret she has spent years hiding, before someone else reveals it for her......</x:v>
+      </x:c>
+      <x:c r="D18" s="9" t="str">
+        <x:v>Romance</x:v>
+      </x:c>
+      <x:c r="E18" s="9" t="str">
+        <x:v>Bodyguard</x:v>
+      </x:c>
+      <x:c r="F18" s="9" t="str">
+        <x:v>Forbidden Love</x:v>
+      </x:c>
+      <x:c r="G18" s="9" t="str">
+        <x:v>Suspense</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A19" s="8" t="str">
         <x:v>9b</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>Deadly Manor Hides the Secrets My Family Buried</x:v>
-      </x:c>
-      <x:c r="C19" s="10"/>
-      <x:c r="D19" s="9"/>
-      <x:c r="E19" s="9"/>
-      <x:c r="F19" s="9"/>
-      <x:c r="G19" s="9"/>
-    </x:row>
-    <x:row r="20" ht="42" customHeight="1">
+        <x:v>My Dear Bodyguard</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str">
+        <x:v>After a threatening message interrupts an awards ceremony, rising singer Serena is assigned a bodyguard who refuses to be charmed by fame. Ethan keeps his distance, follows every rule, and notices details that her closest friends overlook. A kiss meant to distract a photographer changes their arrangement, making the line between protection and desire harder to maintain. When another warning exposes a connection to Serena's past, even the people managing her career become suspects. Forced into an uneasy retreat from public life, she must decide whether to trust Ethan with the secret she has spent years hiding, before someone else reveals it for her......</x:v>
+      </x:c>
+      <x:c r="D19" s="9" t="str">
+        <x:v>Romance</x:v>
+      </x:c>
+      <x:c r="E19" s="9" t="str">
+        <x:v>Bodyguard</x:v>
+      </x:c>
+      <x:c r="F19" s="9" t="str">
+        <x:v>Forbidden Love</x:v>
+      </x:c>
+      <x:c r="G19" s="9" t="str">
+        <x:v>Suspense</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A20" s="8" t="str">
         <x:v>10a</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>Price of Truth</x:v>
-      </x:c>
-      <x:c r="C20" s="10"/>
-      <x:c r="D20" s="9"/>
-      <x:c r="E20" s="9"/>
-      <x:c r="F20" s="9"/>
-      <x:c r="G20" s="9"/>
-    </x:row>
-    <x:row r="21" ht="42" customHeight="1">
+        <x:v>The Price of Truth Changes Who We Call Family</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str">
+        <x:v>A routine request for family medical records leads Nora to a discrepancy nobody is willing to explain. Her parents call it an administrative mistake, while her siblings urge her to stop asking questions before their father's retirement celebration. But an old photograph points to a woman whose name has been removed from every family story. As Nora searches for her, familiar relationships become difficult to recognize, and each answer places someone she loves in a different light. With the celebration approaching, she must decide whether belonging depends on protecting a shared history or accepting the people that history was designed to keep out......</x:v>
+      </x:c>
+      <x:c r="D20" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E20" s="9" t="str">
+        <x:v>Mystery</x:v>
+      </x:c>
+      <x:c r="F20" s="9" t="str">
+        <x:v>Family Secrets</x:v>
+      </x:c>
+      <x:c r="G20" s="9" t="str">
+        <x:v>Betrayal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A21" s="8" t="str">
         <x:v>10b</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>The Price of Truth Changes Who We Call Family</x:v>
-      </x:c>
-      <x:c r="C21" s="10"/>
-      <x:c r="D21" s="9"/>
-      <x:c r="E21" s="9"/>
-      <x:c r="F21" s="9"/>
-      <x:c r="G21" s="9"/>
-    </x:row>
-    <x:row r="22" ht="42" customHeight="1">
+        <x:v>Price of Truth</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="str">
+        <x:v>A routine request for family medical records leads Nora to a discrepancy nobody is willing to explain. Her parents call it an administrative mistake, while her siblings urge her to stop asking questions before their father's retirement celebration. But an old photograph points to a woman whose name has been removed from every family story. As Nora searches for her, familiar relationships become difficult to recognize, and each answer places someone she loves in a different light. With the celebration approaching, she must decide whether belonging depends on protecting a shared history or accepting the people that history was designed to keep out......</x:v>
+      </x:c>
+      <x:c r="D21" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E21" s="9" t="str">
+        <x:v>Mystery</x:v>
+      </x:c>
+      <x:c r="F21" s="9" t="str">
+        <x:v>Family Secrets</x:v>
+      </x:c>
+      <x:c r="G21" s="9" t="str">
+        <x:v>Betrayal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A22" s="8" t="str">
         <x:v>11a</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>Fatal Cover-Up</x:v>
-      </x:c>
-      <x:c r="C22" s="10"/>
-      <x:c r="D22" s="9"/>
-      <x:c r="E22" s="9"/>
-      <x:c r="F22" s="9"/>
-      <x:c r="G22" s="9"/>
-    </x:row>
-    <x:row r="23" ht="42" customHeight="1">
+        <x:v>Power Within Keeps the Family’s Crime Buried</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str">
+        <x:v>When a young accountant disappears after reviewing the family firm's books, Lucas is told to leave the investigation to people who understand what is at stake. Instead, he follows a trail of payments connecting his relatives to a crime that was officially solved years ago. His father insists the business protects the community, while his sister fears that exposing it will endanger everyone they employ. As evidence vanishes and an investigator offers an uneasy alliance, Lucas discovers how easily loyalty can become complicity. To learn what happened to the missing accountant, he must challenge the people who taught him that family always comes first......</x:v>
+      </x:c>
+      <x:c r="D22" s="9" t="str">
+        <x:v>Crime</x:v>
+      </x:c>
+      <x:c r="E22" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="F22" s="9" t="str">
+        <x:v>Suspense</x:v>
+      </x:c>
+      <x:c r="G22" s="9" t="str">
+        <x:v>Corruption</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A23" s="8" t="str">
         <x:v>11b</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>The Fatal Cover-Up Behind My Boyfriend’s Death</x:v>
-      </x:c>
-      <x:c r="C23" s="10"/>
-      <x:c r="D23" s="9"/>
-      <x:c r="E23" s="9"/>
-      <x:c r="F23" s="9"/>
-      <x:c r="G23" s="9"/>
-    </x:row>
-    <x:row r="24" ht="42" customHeight="1">
+        <x:v>Power Within</x:v>
+      </x:c>
+      <x:c r="C23" s="10" t="str">
+        <x:v>When a young accountant disappears after reviewing the family firm's books, Lucas is told to leave the investigation to people who understand what is at stake. Instead, he follows a trail of payments connecting his relatives to a crime that was officially solved years ago. His father insists the business protects the community, while his sister fears that exposing it will endanger everyone they employ. As evidence vanishes and an investigator offers an uneasy alliance, Lucas discovers how easily loyalty can become complicity. To learn what happened to the missing accountant, he must challenge the people who taught him that family always comes first......</x:v>
+      </x:c>
+      <x:c r="D23" s="9" t="str">
+        <x:v>Crime</x:v>
+      </x:c>
+      <x:c r="E23" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="F23" s="9" t="str">
+        <x:v>Suspense</x:v>
+      </x:c>
+      <x:c r="G23" s="9" t="str">
+        <x:v>Corruption</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A24" s="8" t="str">
         <x:v>12a</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>Shattered Trust</x:v>
-      </x:c>
-      <x:c r="C24" s="10"/>
-      <x:c r="D24" s="9"/>
-      <x:c r="E24" s="9"/>
-      <x:c r="F24" s="9"/>
-      <x:c r="G24" s="9"/>
-    </x:row>
-    <x:row r="25" ht="42" customHeight="1">
+        <x:v>When I Returned to the Deadly Manor, I Uncovered the Secrets My Family Buried</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="str">
+        <x:v>Returning to her childhood manor for the reading of a will, Elise expects a brief reunion with relatives she has avoided for years. Instead, the inheritance includes a condition that keeps them under one roof until a missing document is found. Locked rooms, conflicting memories, and a message left in her late mother's handwriting suggest that the family fortune conceals more than financial wrongdoing. When someone begins searching her belongings, Elise realizes that her return was anticipated. With each relative guarding a different part of the past, she must decide whose help to accept before the house gives up a secret someone will do anything to preserve......</x:v>
+      </x:c>
+      <x:c r="D24" s="9" t="str">
+        <x:v>Mystery</x:v>
+      </x:c>
+      <x:c r="E24" s="9" t="str">
+        <x:v>Suspense</x:v>
+      </x:c>
+      <x:c r="F24" s="9" t="str">
+        <x:v>Family Secrets</x:v>
+      </x:c>
+      <x:c r="G24" s="9" t="str">
+        <x:v>Inheritance</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A25" s="8" t="str">
         <x:v>12b</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>Shattered Trust Leads Me Back to My Husband’s Brother</x:v>
-      </x:c>
-      <x:c r="C25" s="10"/>
-      <x:c r="D25" s="9"/>
-      <x:c r="E25" s="9"/>
-      <x:c r="F25" s="9"/>
-      <x:c r="G25" s="9"/>
-    </x:row>
-    <x:row r="26" ht="42" customHeight="1">
+        <x:v>Secrets Buried in the Manor</x:v>
+      </x:c>
+      <x:c r="C25" s="10" t="str">
+        <x:v>Returning to her childhood manor for the reading of a will, Elise expects a brief reunion with relatives she has avoided for years. Instead, the inheritance includes a condition that keeps them under one roof until a missing document is found. Locked rooms, conflicting memories, and a message left in her late mother's handwriting suggest that the family fortune conceals more than financial wrongdoing. When someone begins searching her belongings, Elise realizes that her return was anticipated. With each relative guarding a different part of the past, she must decide whose help to accept before the house gives up a secret someone will do anything to preserve......</x:v>
+      </x:c>
+      <x:c r="D25" s="9" t="str">
+        <x:v>Mystery</x:v>
+      </x:c>
+      <x:c r="E25" s="9" t="str">
+        <x:v>Suspense</x:v>
+      </x:c>
+      <x:c r="F25" s="9" t="str">
+        <x:v>Family Secrets</x:v>
+      </x:c>
+      <x:c r="G25" s="9" t="str">
+        <x:v>Inheritance</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A26" s="8" t="str">
         <x:v>13a</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>Second Shift</x:v>
-      </x:c>
-      <x:c r="C26" s="10"/>
-      <x:c r="D26" s="9"/>
-      <x:c r="E26" s="9"/>
-      <x:c r="F26" s="9"/>
-      <x:c r="G26" s="9"/>
-    </x:row>
-    <x:row r="27" ht="42" customHeight="1">
+        <x:v>After Years in Hiding, the Lost Daughter Returned to a Family Built on Lies</x:v>
+      </x:c>
+      <x:c r="C26" s="10" t="str">
+        <x:v>Years after vanishing from a wealthy household, Grace returns with a different surname and a document that could establish her place in the family. Her arrival unsettles a carefully negotiated succession, particularly the siblings who have built their futures around her absence. While one relative welcomes her, another insists that the woman at the door is an impostor. Grace has reasons for keeping parts of her past private, but every unanswered question weakens her claim. As the family prepares to announce its new leader, she must decide whether proving where she belongs is worth exposing the life she created to survive without them......</x:v>
+      </x:c>
+      <x:c r="D26" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E26" s="9" t="str">
+        <x:v>Lost Heiress</x:v>
+      </x:c>
+      <x:c r="F26" s="9" t="str">
+        <x:v>Reunion</x:v>
+      </x:c>
+      <x:c r="G26" s="9" t="str">
+        <x:v>Hidden Identity</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A27" s="8" t="str">
         <x:v>13b</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>Second Shift Brings Three Siblings Back Behind the Counter</x:v>
-      </x:c>
-      <x:c r="C27" s="10"/>
-      <x:c r="D27" s="9"/>
-      <x:c r="E27" s="9"/>
-      <x:c r="F27" s="9"/>
-      <x:c r="G27" s="9"/>
-    </x:row>
-    <x:row r="28" ht="42" customHeight="1">
+        <x:v>The Lost Daughter Came Home</x:v>
+      </x:c>
+      <x:c r="C27" s="10" t="str">
+        <x:v>Years after vanishing from a wealthy household, Grace returns with a different surname and a document that could establish her place in the family. Her arrival unsettles a carefully negotiated succession, particularly the siblings who have built their futures around her absence. While one relative welcomes her, another insists that the woman at the door is an impostor. Grace has reasons for keeping parts of her past private, but every unanswered question weakens her claim. As the family prepares to announce its new leader, she must decide whether proving where she belongs is worth exposing the life she created to survive without them......</x:v>
+      </x:c>
+      <x:c r="D27" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E27" s="9" t="str">
+        <x:v>Lost Heiress</x:v>
+      </x:c>
+      <x:c r="F27" s="9" t="str">
+        <x:v>Reunion</x:v>
+      </x:c>
+      <x:c r="G27" s="9" t="str">
+        <x:v>Hidden Identity</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A28" s="8" t="str">
         <x:v>14a</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>Last Table</x:v>
-      </x:c>
-      <x:c r="C28" s="10"/>
-      <x:c r="D28" s="9"/>
-      <x:c r="E28" s="9"/>
-      <x:c r="F28" s="9"/>
-      <x:c r="G28" s="9"/>
-    </x:row>
-    <x:row r="29" ht="42" customHeight="1">
+        <x:v>The Next Chapter Starts Here: Building Tomorrow Against the Odds</x:v>
+      </x:c>
+      <x:c r="C28" s="10" t="str">
+        <x:v>After their employer abruptly closes a promising division, four colleagues pool their savings to keep a small development project alive. They have a borrowed office, a skeptical first client, and different ideas about what success should look like. Leading the venture forces Alex to confront the habits that cost him his previous job, while his partners balance mounting bills with commitments outside work. An investor's offer could secure their future, but its terms would change the purpose of everything they have built. With a crucial presentation approaching, the team must decide what they are prepared to compromise and what makes this new beginning worth protecting......</x:v>
+      </x:c>
+      <x:c r="D28" s="9" t="str">
+        <x:v>Drama</x:v>
+      </x:c>
+      <x:c r="E28" s="9" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+      <x:c r="F28" s="9" t="str">
+        <x:v>Friendship</x:v>
+      </x:c>
+      <x:c r="G28" s="9" t="str">
+        <x:v>Ambition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A29" s="8" t="str">
         <x:v>14b</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>Last Table Brings Three Generations Back to the Diner</x:v>
-      </x:c>
-      <x:c r="C29" s="10"/>
-      <x:c r="D29" s="9"/>
-      <x:c r="E29" s="9"/>
-      <x:c r="F29" s="9"/>
-      <x:c r="G29" s="9"/>
-    </x:row>
-    <x:row r="30" ht="42" customHeight="1">
+        <x:v>The Next Chapter</x:v>
+      </x:c>
+      <x:c r="C29" s="10" t="str">
+        <x:v>After their employer abruptly closes a promising division, four colleagues pool their savings to keep a small development project alive. They have a borrowed office, a skeptical first client, and different ideas about what success should look like. Leading the venture forces Alex to confront the habits that cost him his previous job, while his partners balance mounting bills with commitments outside work. An investor's offer could secure their future, but its terms would change the purpose of everything they have built. With a crucial presentation approaching, the team must decide what they are prepared to compromise and what makes this new beginning worth protecting......</x:v>
+      </x:c>
+      <x:c r="D29" s="9" t="str">
+        <x:v>Drama</x:v>
+      </x:c>
+      <x:c r="E29" s="9" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+      <x:c r="F29" s="9" t="str">
+        <x:v>Friendship</x:v>
+      </x:c>
+      <x:c r="G29" s="9" t="str">
+        <x:v>Ambition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A30" s="8" t="str">
         <x:v>15a</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>New House Rules</x:v>
-      </x:c>
-      <x:c r="C30" s="10"/>
-      <x:c r="D30" s="9"/>
-      <x:c r="E30" s="9"/>
-      <x:c r="F30" s="9"/>
-      <x:c r="G30" s="9"/>
-    </x:row>
-    <x:row r="31" ht="42" customHeight="1">
+        <x:v>The Son We Lost Returned With the Truth Our Family Tried to Hide</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="str">
+        <x:v>A stranger arrives at a family memorial carrying the childhood watch of a son presumed lost many years earlier. He claims to be that son, but his memories contradict the account his parents have repeated since his disappearance. His return offers hope to his mother and threatens the brother preparing to inherit the family business. While they wait for proof of his identity, a forgotten witness begins asking questions of her own. The man wants more than a welcome home, and someone in the household already knows why. Before the family can reunite, they must confront what happened on the night they stopped searching......</x:v>
+      </x:c>
+      <x:c r="D30" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E30" s="9" t="str">
+        <x:v>Reunion</x:v>
+      </x:c>
+      <x:c r="F30" s="9" t="str">
+        <x:v>Family Secrets</x:v>
+      </x:c>
+      <x:c r="G30" s="9" t="str">
+        <x:v>Mystery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A31" s="8" t="str">
         <x:v>15b</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>New House Rules Turn Our Blended Family Upside Down</x:v>
-      </x:c>
-      <x:c r="C31" s="10"/>
-      <x:c r="D31" s="9"/>
-      <x:c r="E31" s="9"/>
-      <x:c r="F31" s="9"/>
-      <x:c r="G31" s="9"/>
-    </x:row>
-    <x:row r="32" ht="42" customHeight="1">
+        <x:v>The Missing Son Returns</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="str">
+        <x:v>A stranger arrives at a family memorial carrying the childhood watch of a son presumed lost many years earlier. He claims to be that son, but his memories contradict the account his parents have repeated since his disappearance. His return offers hope to his mother and threatens the brother preparing to inherit the family business. While they wait for proof of his identity, a forgotten witness begins asking questions of her own. The man wants more than a welcome home, and someone in the household already knows why. Before the family can reunite, they must confront what happened on the night they stopped searching......</x:v>
+      </x:c>
+      <x:c r="D31" s="9" t="str">
+        <x:v>Family Drama</x:v>
+      </x:c>
+      <x:c r="E31" s="9" t="str">
+        <x:v>Reunion</x:v>
+      </x:c>
+      <x:c r="F31" s="9" t="str">
+        <x:v>Family Secrets</x:v>
+      </x:c>
+      <x:c r="G31" s="9" t="str">
+        <x:v>Mystery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A32" s="8" t="str">
         <x:v>16a</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>Shared Custody</x:v>
-      </x:c>
-      <x:c r="C32" s="10"/>
-      <x:c r="D32" s="9"/>
-      <x:c r="E32" s="9"/>
-      <x:c r="F32" s="9"/>
-      <x:c r="G32" s="9"/>
-    </x:row>
-    <x:row r="33" ht="42" customHeight="1">
+        <x:v>When My Boss Stole My Promotion, I Exposed the Lies That Built His Empire</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="str">
+        <x:v>When his boss presents his work as his own and awards his promotion to a well connected colleague, analyst Ryan decides to leave quietly. Then a misplaced report reveals that his stolen project is part of a much larger deception. Searching for evidence draws him into an alliance with coworkers who have their own reasons to remain silent. His boss offers a deal that could restore his career, provided he abandons the investigation. With a public launch approaching and his reputation already under attack, Ryan must decide whether exposing the truth will change the company or simply give its most powerful people another person to blame......</x:v>
+      </x:c>
+      <x:c r="D32" s="9" t="str">
+        <x:v>Drama</x:v>
+      </x:c>
+      <x:c r="E32" s="9" t="str">
+        <x:v>Workplace</x:v>
+      </x:c>
+      <x:c r="F32" s="9" t="str">
+        <x:v>Revenge</x:v>
+      </x:c>
+      <x:c r="G32" s="9" t="str">
+        <x:v>Corruption</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A33" s="8" t="str">
         <x:v>16b</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>Shared Custody Puts Two Households Under One Roof</x:v>
-      </x:c>
-      <x:c r="C33" s="10"/>
-      <x:c r="D33" s="9"/>
-      <x:c r="E33" s="9"/>
-      <x:c r="F33" s="9"/>
-      <x:c r="G33" s="9"/>
+        <x:v>Exposed the Lies of My Boss</x:v>
+      </x:c>
+      <x:c r="C33" s="10" t="str">
+        <x:v>When his boss presents his work as his own and awards his promotion to a well connected colleague, analyst Ryan decides to leave quietly. Then a misplaced report reveals that his stolen project is part of a much larger deception. Searching for evidence draws him into an alliance with coworkers who have their own reasons to remain silent. His boss offers a deal that could restore his career, provided he abandons the investigation. With a public launch approaching and his reputation already under attack, Ryan must decide whether exposing the truth will change the company or simply give its most powerful people another person to blame......</x:v>
+      </x:c>
+      <x:c r="D33" s="9" t="str">
+        <x:v>Drama</x:v>
+      </x:c>
+      <x:c r="E33" s="9" t="str">
+        <x:v>Workplace</x:v>
+      </x:c>
+      <x:c r="F33" s="9" t="str">
+        <x:v>Revenge</x:v>
+      </x:c>
+      <x:c r="G33" s="9" t="str">
+        <x:v>Corruption</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ddbb048a5114bd6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52a37a46339c44c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>